--- a/回後買上漲圖表_20260617/回後買上漲_標準版(1+2)_20260617.xlsx
+++ b/回後買上漲圖表_20260617/回後買上漲_標準版(1+2)_20260617.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -561,28 +561,28 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>5508.TWO</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>永信建</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>42.55</v>
+        <v>61.1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>40.5</v>
+        <v>57.3</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>192085</v>
+        <v>3685</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>43046</v>
+        <v>853</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>未踩支撐</t>
+          <t>踩10MA</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
@@ -603,28 +603,28 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>5508.TWO</t>
+          <t>5905.TWO</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>永信建</t>
+          <t>南仁湖</t>
         </is>
       </c>
       <c r="C3" s="9" t="n">
-        <v>61.1</v>
+        <v>8.9</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>57.3</v>
+        <v>8.51</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>3685</v>
+        <v>2352</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>853</v>
+        <v>713</v>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
@@ -645,28 +645,28 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>6177.TW</t>
+          <t>4542.TWO</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>科嶠</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>48.25</v>
+        <v>378</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>47.45</v>
+        <v>365</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>2948</v>
+        <v>411</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>751</v>
+        <v>202</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>踩10MA</t>
+          <t>未踩支撐</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
@@ -687,28 +687,28 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>5534.TW</t>
+          <t>4923.TWO</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>長虹</t>
+          <t>力士</t>
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>85.2</v>
+        <v>52.5</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>83.2</v>
+        <v>51.3</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2867</v>
+        <v>2682</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>801</v>
+        <v>1567</v>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
@@ -721,426 +721,6 @@
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5905.TWO</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>南仁湖</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>8.51</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>2352</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>713</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>2610.TW</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>華航</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>152601</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>58755</v>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>未踩支撐</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2439.TW</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>美律</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>4749</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>1899</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>2520.TW</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>冠德</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>36.15</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>35.25</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>4808</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>2185</v>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>4542.TWO</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>科嶠</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>378</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>365</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>411</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>202</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>未踩支撐</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>2495.TW</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>普安</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>52</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>20074</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>11296</v>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2241.TW</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>艾姆勒</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>46.05</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>45.05</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>5026</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>2907</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>未踩支撐</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>6269.TW</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>台郡</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>21347</v>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>12736</v>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>4923.TWO</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>力士</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>2682</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>1567</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>未踩支撐</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>3653.TW</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>3990</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>3950</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>1549</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>1007</v>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -1152,16 +732,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
